--- a/assets/constructions/examples/ctd_tsmb_multi_functional.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_multi_functional.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM3"/>
+  <dimension ref="A1:AR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,11 +624,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PICCO L-MFT60 6-4 L08 IC908</t>
+          <t>PICCO L-MFT60 8-8 L16 IC908</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -654,16 +679,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -672,7 +697,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>7.9</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
@@ -686,10 +711,10 @@
         <v>60</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="W2" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
@@ -700,7 +725,7 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ISCAR_PICCO:6</t>
+          <t>ISCAR_PICCO:8</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -737,11 +762,22 @@
           <t>2020 / ISCAR</t>
         </is>
       </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PICCO L-MFT60 8-8 L16 IC908</t>
+          <t>PICCO L-MFT60 6-4 L08 IC908</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -767,16 +803,16 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
         <v>8</v>
       </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>16</v>
-      </c>
       <c r="K3" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -785,7 +821,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7.9</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
@@ -799,10 +835,10 @@
         <v>60</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
@@ -813,7 +849,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ISCAR_PICCO:8</t>
+          <t>ISCAR_PICCO:6</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -848,6 +884,17 @@
       <c r="AM3" t="inlineStr">
         <is>
           <t>2020 / ISCAR</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
